--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E96C558D-A7C5-4FB0-BB98-E1AF400460EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00330A8B-7470-4ED9-ACE8-D5B77FBB2772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00330A8B-7470-4ED9-ACE8-D5B77FBB2772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA4825E9-653E-408E-9FDE-5A4A084A3DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA4825E9-653E-408E-9FDE-5A4A084A3DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DD384CD-F585-4505-ADFB-A23892744187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DD384CD-F585-4505-ADFB-A23892744187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5D63916-9B06-4197-8FB7-7C0C72C88B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
